--- a/ui_runner/templates/graded_analysis_tabs_2026-05-10.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-10.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>53.6</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="3">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>54.8</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="5">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="6">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4985</v>
+        <v>5094</v>
       </c>
       <c r="E8" t="n">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="F8" t="n">
-        <v>4181</v>
+        <v>4278</v>
       </c>
       <c r="G8" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="G9" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="E10" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="F10" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G10" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="E11" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="F11" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G11" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="12">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E13" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G13" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E14" t="n">
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G14" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F15" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G15" t="n">
-        <v>24.3</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2342</v>
+        <v>2337</v>
       </c>
       <c r="E17" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F17" t="n">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="G17" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
     </row>
   </sheetData>
@@ -1112,10 +1112,10 @@
         <v>55</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
         <v>33.3</v>
@@ -1124,10 +1124,10 @@
         <v>30</v>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J2" t="n">
         <v>14.3</v>
@@ -1145,19 +1145,19 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R2" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1166,34 +1166,34 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="Y2" t="n">
         <v>990</v>
       </c>
       <c r="Z2" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>85</v>
+        <v>81.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AD2" t="n">
         <v>100</v>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="n">
-        <v>60</v>
+        <v>65.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -1215,10 +1215,10 @@
         <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3" t="n">
         <v>50.8</v>
@@ -1239,22 +1239,22 @@
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>21.7</v>
+        <v>23.8</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
-        <v>35.4</v>
+        <v>34.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R3" t="n">
-        <v>62.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -1266,16 +1266,16 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>557</v>
+        <v>662</v>
       </c>
       <c r="Z3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
         <v>60</v>
@@ -1290,10 +1290,10 @@
         <v>4</v>
       </c>
       <c r="AF3" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="Y4" t="n">
         <v>1350</v>
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>65.8</v>
+        <v>68.3</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>67.59999999999999</v>
@@ -1388,40 +1388,40 @@
         <v>34</v>
       </c>
       <c r="H5" t="n">
-        <v>64.5</v>
+        <v>63.3</v>
       </c>
       <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
+      <c r="L5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="M5" t="n">
         <v>31</v>
       </c>
-      <c r="J5" t="n">
-        <v>50</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>28</v>
-      </c>
       <c r="N5" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="O5" t="n">
+        <v>21</v>
+      </c>
+      <c r="P5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="n">
         <v>20</v>
       </c>
-      <c r="P5" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>21</v>
-      </c>
       <c r="R5" t="n">
-        <v>92.3</v>
+        <v>93.3</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1433,16 +1433,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="Z5" t="n">
-        <v>57.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
         <v>50</v>
@@ -1457,10 +1457,10 @@
         <v>4</v>
       </c>
       <c r="AF5" t="n">
-        <v>51.8</v>
+        <v>46.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.6</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8</v>
+        <v>64.3</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
         <v>57.1</v>
@@ -1500,16 +1500,16 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>35</v>
+        <v>33.3</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="O6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
         <v>20</v>
@@ -1517,41 +1517,44 @@
       <c r="Q6" t="n">
         <v>5</v>
       </c>
+      <c r="R6" t="n">
+        <v>100</v>
+      </c>
       <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>835</v>
+        <v>910</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -1561,16 +1564,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="C7" t="n">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="D7" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="E7" t="n">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="F7" t="n">
         <v>60.8</v>
@@ -1579,46 +1582,46 @@
         <v>263</v>
       </c>
       <c r="H7" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="I7" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="J7" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="K7" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L7" t="n">
-        <v>24.3</v>
+        <v>25.2</v>
       </c>
       <c r="M7" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="N7" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
       <c r="O7" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="P7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2342</v>
+        <v>2337</v>
       </c>
       <c r="R7" t="n">
-        <v>53.6</v>
+        <v>59.5</v>
       </c>
       <c r="S7" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="T7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="U7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V7" t="n">
         <v>53.8</v>
@@ -1627,34 +1630,34 @@
         <v>26</v>
       </c>
       <c r="X7" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>4985</v>
+        <v>5094</v>
       </c>
       <c r="Z7" t="n">
-        <v>54.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="AB7" t="n">
-        <v>60</v>
+        <v>59.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="AG7" t="n">
-        <v>276</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/ui_runner/templates/graded_analysis_tabs_2026-05-10.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-05-10.xlsx
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5094</v>
+        <v>5100</v>
       </c>
       <c r="E8" t="n">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F8" t="n">
-        <v>4278</v>
+        <v>4282</v>
       </c>
       <c r="G8" t="n">
         <v>16</v>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="Y3" t="n">
         <v>662</v>
@@ -1342,7 +1342,7 @@
         <v>12.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="Z4" t="n">
         <v>62.5</v>
@@ -1633,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>5094</v>
+        <v>5100</v>
       </c>
       <c r="Z7" t="n">
         <v>64.59999999999999</v>
